--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486860_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486860_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1166</v>
+        <v>7.407</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2713</v>
+        <v>6.0359</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8453</v>
+        <v>1.3711</v>
       </c>
       <c r="G2" t="n">
         <v>5.4538</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>4.0037</v>
+        <v>1.2941</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4014</v>
+        <v>1.166</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6024</v>
+        <v>0.1281</v>
       </c>
       <c r="V2" t="n">
         <v>1.0698</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9987</v>
+        <v>2.9822</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7489</v>
+        <v>1.8806</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2498</v>
+        <v>1.1016</v>
       </c>
       <c r="G3" t="n">
         <v>0.6636</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0407</v>
+        <v>-0.0571</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0854</v>
+        <v>0.0464</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0447</v>
+        <v>-0.1035</v>
       </c>
       <c r="V3" t="n">
         <v>0.9384</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5788</v>
+        <v>1.0565</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2585</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3203</v>
+        <v>0.3796</v>
       </c>
       <c r="G4" t="n">
         <v>2.8337</v>
@@ -766,13 +766,13 @@
         <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8709</v>
+        <v>-0.3932</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3216</v>
+        <v>0.0968</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5493</v>
+        <v>-0.49</v>
       </c>
       <c r="V4" t="n">
         <v>-1.1786</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>J. GOLSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0475</v>
+        <v>0.3757</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1976</v>
+        <v>-0.1186</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1502</v>
+        <v>0.4943</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0843</v>
+        <v>0.7073</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1947</v>
+        <v>0.9337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2789</v>
+        <v>-0.2264</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.1795</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.0618</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.1177</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0843</v>
+        <v>-0.4722</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1947</v>
+        <v>0.8719</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2789</v>
+        <v>-1.3441</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1317</v>
+        <v>-0.8824</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1976</v>
+        <v>-0.2714</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0659</v>
+        <v>-0.611</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.476</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5185</v>
+        <v>0.1151</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8179</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2994</v>
+        <v>-0.6657</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1822</v>
+        <v>1.9287</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7754</v>
+        <v>-2.2677</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9576</v>
+        <v>4.1964</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0841</v>
+        <v>2.6669</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3363</v>
+        <v>-2.1081</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4204</v>
+        <v>4.775</v>
       </c>
       <c r="M6" t="n">
-        <v>0.098</v>
+        <v>-0.7381</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5609</v>
+        <v>-0.1596</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4629</v>
+        <v>-0.5786</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.616</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8489</v>
+        <v>-0.4978</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8486</v>
+        <v>0.0154</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0002</v>
+        <v>-0.5132</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2357</v>
+        <v>0.9429</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X6" t="n">
         <v>-0.2357</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6896</v>
+        <v>0.0184</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0832</v>
+        <v>-0.1317</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6064000000000001</v>
+        <v>0.1502</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9287</v>
+        <v>0.0843</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2677</v>
+        <v>-0.1947</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1964</v>
+        <v>0.2789</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6669</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1081</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4.775</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7381</v>
+        <v>0.0843</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1596</v>
+        <v>-0.1947</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5786</v>
+        <v>0.2789</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3025</v>
+        <v>-0.0659</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8486</v>
+        <v>-0.1317</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4539</v>
+        <v>0.0659</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9429</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0257</v>
+        <v>-0.3389</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1512</v>
+        <v>-1.6087</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1256</v>
+        <v>1.2698</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.7802</v>
+        <v>1.1822</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.4514</v>
+        <v>-0.7754</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3288</v>
+        <v>1.9576</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.3839</v>
+        <v>1.0841</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.5417</v>
+        <v>-1.3363</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1579</v>
+        <v>2.4204</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3963</v>
+        <v>0.098</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.5609</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4866</v>
+        <v>-0.4629</v>
       </c>
       <c r="P8" t="n">
         <v>-0.616</v>
@@ -1078,19 +1078,19 @@
         <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1874</v>
+        <v>-0.6693</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8672</v>
+        <v>-0.6394</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3202</v>
+        <v>-0.0299</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1831</v>
+        <v>-0.2357</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>-0.2357</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GOLSON</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3653</v>
+        <v>-3.0097</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2964</v>
+        <v>-3.7203</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0689</v>
+        <v>0.7106</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7073</v>
+        <v>-3.7802</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9337</v>
+        <v>-3.4514</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2264</v>
+        <v>-0.3288</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1795</v>
+        <v>-3.3839</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0618</v>
+        <v>-3.5417</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1177</v>
+        <v>0.1579</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4722</v>
+        <v>-0.3963</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8719</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3441</v>
+        <v>-0.4866</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0267</v>
+        <v>-0.616</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.6233</v>
+        <v>0.2034</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4492</v>
+        <v>0.2982</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1742</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.476</v>
+        <v>1.1831</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.476</v>
+        <v>-0.2357</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6723</v>
+        <v>-3.2176</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4822</v>
+        <v>-2.9979</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.19</v>
+        <v>-0.2197</v>
       </c>
       <c r="G10" t="n">
         <v>0.4134</v>
@@ -1234,13 +1234,13 @@
         <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.907</v>
+        <v>-0.4524</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1857</v>
+        <v>-0.7014</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2787</v>
+        <v>0.249</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3573</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.4886</v>
+        <v>-9.8432</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.016</v>
+        <v>-9.9041</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4727</v>
+        <v>0.0609</v>
       </c>
       <c r="G11" t="n">
         <v>-7.5904</v>
@@ -1312,13 +1312,13 @@
         <v>2.4641</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.217</v>
+        <v>-0.5715</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5151</v>
+        <v>-0.4032</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7019</v>
+        <v>-0.1683</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0653</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1134</v>
+        <v>-4.454499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.7658</v>
+        <v>-9.107199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>4.6526</v>
+        <v>4.652699999999999</v>
       </c>
       <c r="G12" t="n">
         <v>1.896399999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.326300000000001</v>
+        <v>-3.326299999999999</v>
       </c>
       <c r="I12" t="n">
         <v>5.222599999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>3.545</v>
+        <v>3.544999999999998</v>
       </c>
       <c r="K12" t="n">
         <v>-5.6088</v>
@@ -1390,10 +1390,10 @@
         <v>14.374</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.7509</v>
+        <v>-2.092099999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1832</v>
+        <v>-0.5243000000000002</v>
       </c>
       <c r="U12" t="n">
         <v>-1.5676</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6715</v>
+        <v>4.8476</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2608</v>
+        <v>4.0516</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4107</v>
+        <v>0.796</v>
       </c>
       <c r="G13" t="n">
         <v>0.5421</v>
@@ -1468,13 +1468,13 @@
         <v>0.8214</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3614</v>
+        <v>0.5375</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1122</v>
+        <v>-0.097</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2492</v>
+        <v>0.6345</v>
       </c>
       <c r="V13" t="n">
         <v>2.9466</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1293</v>
+        <v>3.4721</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9354</v>
+        <v>0.3078</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1939</v>
+        <v>3.1643</v>
       </c>
       <c r="G14" t="n">
         <v>2.5094</v>
@@ -1546,13 +1546,13 @@
         <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6384</v>
+        <v>0.9812</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1117</v>
+        <v>0.4841</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.4971</v>
       </c>
       <c r="V14" t="n">
         <v>1.4189</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0775</v>
+        <v>1.4837</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2594</v>
+        <v>-0.5272</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3369</v>
+        <v>2.0109</v>
       </c>
       <c r="G15" t="n">
         <v>0.3533</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.132</v>
+        <v>0.2742</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0462</v>
+        <v>-0.314</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9142</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.2402</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8408</v>
+        <v>1.0709</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4651</v>
+        <v>0.6743</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3757</v>
+        <v>0.3966</v>
       </c>
       <c r="G16" t="n">
         <v>0.2658</v>
@@ -1702,13 +1702,13 @@
         <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1108</v>
+        <v>0.3409</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3176</v>
+        <v>0.5268</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2067</v>
+        <v>-0.1858</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1786</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. NDOUR</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8188</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.789</v>
+        <v>-0.5508</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9702</v>
+        <v>1.4677</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2507</v>
+        <v>-1.3699</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6069</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8575</v>
+        <v>-1.3602</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1694</v>
+        <v>-1.0204</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3801</v>
+        <v>-0.4019</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7893</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4201</v>
+        <v>-0.3495</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2268</v>
+        <v>0.3923</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6468</v>
+        <v>-0.7418</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6588</v>
+        <v>0.2518</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4328</v>
+        <v>0.2827</v>
       </c>
       <c r="U17" t="n">
-        <v>0.226</v>
+        <v>-0.0309</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1786</v>
+        <v>1.4189</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>K. OBIEKWE SAM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5542</v>
+        <v>0.1906</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6555</v>
+        <v>-0.4689</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2096</v>
+        <v>0.6595</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3699</v>
+        <v>-1.6031</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-1.2717</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3602</v>
+        <v>-0.3314</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0204</v>
+        <v>-0.6934</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4019</v>
+        <v>-1.2195</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0.5261</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3495</v>
+        <v>-0.9097</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3923</v>
+        <v>-0.0522</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7418</v>
+        <v>-0.8575</v>
       </c>
       <c r="P18" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>2.2588</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1108</v>
+        <v>-0.0194</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1781</v>
+        <v>0.4299</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2889</v>
+        <v>-0.4493</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4189</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. OBIEKWE SAM</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2464</v>
+        <v>-0.0154</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1551</v>
+        <v>-0.9103</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4015</v>
+        <v>0.895</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6031</v>
+        <v>0.8758</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2717</v>
+        <v>0.7363</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3314</v>
+        <v>0.1395</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6934</v>
+        <v>0.0389</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2195</v>
+        <v>0.0389</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5261</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9097</v>
+        <v>0.8368</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0522</v>
+        <v>0.6974</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8575</v>
+        <v>0.1395</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2588</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0364</v>
+        <v>0.1356</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7437</v>
+        <v>0.0775</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7074</v>
+        <v>0.0581</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3431</v>
+        <v>-0.8701</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1195</v>
+        <v>-0.5967</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7764</v>
+        <v>-0.2734</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8758</v>
+        <v>-0.0747</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7363</v>
+        <v>1.1806</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1395</v>
+        <v>-1.2552</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0389</v>
+        <v>-0.1703</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0389</v>
+        <v>0.6458</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.8161</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8368</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6974</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1395</v>
+        <v>-0.4391</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0267</v>
+        <v>1.0267</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1922</v>
+        <v>0.186</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1317</v>
+        <v>-0.221</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0604</v>
+        <v>0.407</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.0082</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>O. NDOUR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2606</v>
+        <v>-1.0797</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2243</v>
+        <v>-0.1984</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0363</v>
+        <v>-0.8813</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0747</v>
+        <v>-0.2507</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1806</v>
+        <v>0.6069</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2552</v>
+        <v>-0.8575</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1703</v>
+        <v>1.1694</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6458</v>
+        <v>0.3801</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8161</v>
+        <v>0.7893</v>
       </c>
       <c r="M21" t="n">
-        <v>0.09569999999999999</v>
+        <v>-1.4201</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.2268</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4391</v>
+        <v>-1.6468</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0267</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2053</v>
+        <v>-2.0534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2045</v>
+        <v>0.7603</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8486</v>
+        <v>0.4454</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6442</v>
+        <v>0.3149</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0082</v>
+        <v>-1.1786</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0082</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2234</v>
+        <v>-1.4423</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.131</v>
+        <v>-1.6079</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0924</v>
+        <v>0.1656</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9308999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2925</v>
+        <v>-0.5114</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.651</v>
+        <v>-0.128</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6415</v>
+        <v>-0.3834</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3981</v>
+        <v>-2.7636</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5583</v>
+        <v>-4.8261</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1601</v>
+        <v>2.0625</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2134</v>
@@ -2248,13 +2248,13 @@
         <v>2.2588</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1231</v>
+        <v>0.5114</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.651</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5279</v>
+        <v>0.4302</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2402</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.113300000000001</v>
+        <v>5.810600000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6528</v>
+        <v>-4.652600000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>9.7659</v>
+        <v>10.4634</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8963</v>
@@ -2302,7 +2302,7 @@
         <v>1.6488</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2825</v>
+        <v>-2.282499999999999</v>
       </c>
       <c r="L24" t="n">
         <v>3.9312</v>
@@ -2311,7 +2311,7 @@
         <v>-3.5451</v>
       </c>
       <c r="N24" t="n">
-        <v>5.6087</v>
+        <v>5.608700000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-9.153700000000001</v>
@@ -2326,19 +2326,19 @@
         <v>17.4542</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7507</v>
+        <v>3.4481</v>
       </c>
       <c r="T24" t="n">
         <v>1.5676</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1833</v>
+        <v>1.8806</v>
       </c>
       <c r="V24" t="n">
         <v>1.1788</v>
       </c>
       <c r="W24" t="n">
-        <v>6.505000000000001</v>
+        <v>6.505</v>
       </c>
       <c r="X24" t="n">
         <v>-5.3264</v>
